--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/80.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/80.xlsx
@@ -426,13 +426,13 @@
         <v>-6.278947471960216</v>
       </c>
       <c r="E2">
-        <v>-9.252974146418344</v>
+        <v>-7.89677769365321</v>
       </c>
       <c r="F2">
-        <v>-6.652777391487973</v>
+        <v>-6.839967301151891</v>
       </c>
       <c r="G2">
-        <v>-10.43788970289278</v>
+        <v>-8.903908700725008</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.607564724208677</v>
       </c>
       <c r="E3">
-        <v>-9.889482867514467</v>
+        <v>-9.071246484490532</v>
       </c>
       <c r="F3">
-        <v>-6.715751123999896</v>
+        <v>-6.800010999477856</v>
       </c>
       <c r="G3">
-        <v>-9.69486424096768</v>
+        <v>-8.95223273396175</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-7.061903176515414</v>
       </c>
       <c r="E4">
-        <v>-10.35223404093628</v>
+        <v>-8.506989566186791</v>
       </c>
       <c r="F4">
-        <v>-7.009249564302087</v>
+        <v>-6.760233625162827</v>
       </c>
       <c r="G4">
-        <v>-9.917425596481804</v>
+        <v>-9.127340729715961</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.569042765644686</v>
       </c>
       <c r="E5">
-        <v>-12.77240451875158</v>
+        <v>-9.8746249442953</v>
       </c>
       <c r="F5">
-        <v>-6.530883542349728</v>
+        <v>-6.804475899778946</v>
       </c>
       <c r="G5">
-        <v>-9.981120492657382</v>
+        <v>-8.78757281992948</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.098761965861769</v>
       </c>
       <c r="E6">
-        <v>-12.15424970280854</v>
+        <v>-10.99967902676092</v>
       </c>
       <c r="F6">
-        <v>-6.767053988173776</v>
+        <v>-6.500235605180952</v>
       </c>
       <c r="G6">
-        <v>-10.21642082740662</v>
+        <v>-8.67405752393341</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.606444363207343</v>
       </c>
       <c r="E7">
-        <v>-13.88406337510251</v>
+        <v>-11.95194465498988</v>
       </c>
       <c r="F7">
-        <v>-6.513409960355075</v>
+        <v>-6.362546446406125</v>
       </c>
       <c r="G7">
-        <v>-9.519143794288706</v>
+        <v>-8.607495695320823</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-9.046031411408274</v>
       </c>
       <c r="E8">
-        <v>-13.18928225047569</v>
+        <v>-12.94234003436341</v>
       </c>
       <c r="F8">
-        <v>-6.128007055998188</v>
+        <v>-6.431104203580318</v>
       </c>
       <c r="G8">
-        <v>-9.663841118719171</v>
+        <v>-8.574045943192028</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-9.386311839655962</v>
       </c>
       <c r="E9">
-        <v>-14.69989966690238</v>
+        <v>-13.50600825104616</v>
       </c>
       <c r="F9">
-        <v>-6.485078138444526</v>
+        <v>-6.301920307113736</v>
       </c>
       <c r="G9">
-        <v>-10.68785244383545</v>
+        <v>-7.88672703105624</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-9.599874779863098</v>
       </c>
       <c r="E10">
-        <v>-16.27585390631174</v>
+        <v>-13.5091011987934</v>
       </c>
       <c r="F10">
-        <v>-6.299352782348759</v>
+        <v>-6.17548162022003</v>
       </c>
       <c r="G10">
-        <v>-9.548111067757327</v>
+        <v>-7.675262624189753</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.672379262200113</v>
       </c>
       <c r="E11">
-        <v>-16.47915068993809</v>
+        <v>-15.20701630017734</v>
       </c>
       <c r="F11">
-        <v>-5.926388228728608</v>
+        <v>-6.318915506933272</v>
       </c>
       <c r="G11">
-        <v>-8.84635155597924</v>
+        <v>-7.684806926979473</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.61134073881014</v>
       </c>
       <c r="E12">
-        <v>-16.43150208642938</v>
+        <v>-15.64315816033008</v>
       </c>
       <c r="F12">
-        <v>-5.892802900749505</v>
+        <v>-6.15603818054152</v>
       </c>
       <c r="G12">
-        <v>-9.267479432938849</v>
+        <v>-6.75939689020484</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.423120621089367</v>
       </c>
       <c r="E13">
-        <v>-17.00836174789647</v>
+        <v>-16.44929898927952</v>
       </c>
       <c r="F13">
-        <v>-5.817791747323801</v>
+        <v>-6.135685193454736</v>
       </c>
       <c r="G13">
-        <v>-9.459140156389415</v>
+        <v>-6.698807285745099</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.136826305468924</v>
       </c>
       <c r="E14">
-        <v>-17.95906505259277</v>
+        <v>-17.60293679968156</v>
       </c>
       <c r="F14">
-        <v>-5.190696085852102</v>
+        <v>-5.585071037548711</v>
       </c>
       <c r="G14">
-        <v>-8.663526678572989</v>
+        <v>-6.000116649681915</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.777939120010725</v>
       </c>
       <c r="E15">
-        <v>-19.44805447715883</v>
+        <v>-18.12877414450423</v>
       </c>
       <c r="F15">
-        <v>-5.461631869020542</v>
+        <v>-5.528115808401828</v>
       </c>
       <c r="G15">
-        <v>-8.154156210264105</v>
+        <v>-5.45069520143893</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-8.374396228343883</v>
       </c>
       <c r="E16">
-        <v>-19.89179058822244</v>
+        <v>-19.74688394845099</v>
       </c>
       <c r="F16">
-        <v>-4.872971626671339</v>
+        <v>-5.192771974563518</v>
       </c>
       <c r="G16">
-        <v>-7.135544384922372</v>
+        <v>-5.263450745737751</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.963043854589509</v>
       </c>
       <c r="E17">
-        <v>-20.61357953183101</v>
+        <v>-20.01546321337192</v>
       </c>
       <c r="F17">
-        <v>-5.187961645055461</v>
+        <v>-5.278208960120857</v>
       </c>
       <c r="G17">
-        <v>-6.999656422171907</v>
+        <v>-4.738586924305079</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-7.564182557865426</v>
       </c>
       <c r="E18">
-        <v>-21.97717098265067</v>
+        <v>-21.35010412986054</v>
       </c>
       <c r="F18">
-        <v>-4.643571841814071</v>
+        <v>-4.83919246071998</v>
       </c>
       <c r="G18">
-        <v>-7.062791836151348</v>
+        <v>-4.893666119546699</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-7.210605466983306</v>
       </c>
       <c r="E19">
-        <v>-22.40476761235093</v>
+        <v>-21.91198812778426</v>
       </c>
       <c r="F19">
-        <v>-4.514858458032278</v>
+        <v>-4.70632232931094</v>
       </c>
       <c r="G19">
-        <v>-6.432718877480638</v>
+        <v>-4.391671546699312</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.922462812634409</v>
       </c>
       <c r="E20">
-        <v>-24.09861614407598</v>
+        <v>-23.37127981980802</v>
       </c>
       <c r="F20">
-        <v>-4.022332737880165</v>
+        <v>-4.550538727173062</v>
       </c>
       <c r="G20">
-        <v>-6.208244026644816</v>
+        <v>-4.567875333027022</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-6.710461378714943</v>
       </c>
       <c r="E21">
-        <v>-24.18288651688472</v>
+        <v>-24.16072869356519</v>
       </c>
       <c r="F21">
-        <v>-3.508746604879277</v>
+        <v>-3.968772158349955</v>
       </c>
       <c r="G21">
-        <v>-6.349306372073161</v>
+        <v>-4.124480726770274</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.587215413923205</v>
       </c>
       <c r="E22">
-        <v>-24.81821783473885</v>
+        <v>-25.08990363282904</v>
       </c>
       <c r="F22">
-        <v>-3.407690751942154</v>
+        <v>-3.822105567847288</v>
       </c>
       <c r="G22">
-        <v>-7.431503845587677</v>
+        <v>-4.50020116111324</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.540582632988596</v>
       </c>
       <c r="E23">
-        <v>-25.5961960838346</v>
+        <v>-25.51243290011472</v>
       </c>
       <c r="F23">
-        <v>-3.487817074080145</v>
+        <v>-3.805255746506944</v>
       </c>
       <c r="G23">
-        <v>-6.057597651880281</v>
+        <v>-4.235453523792184</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-6.564105543331192</v>
       </c>
       <c r="E24">
-        <v>-26.40204256197354</v>
+        <v>-25.70238427084046</v>
       </c>
       <c r="F24">
-        <v>-3.36299121851969</v>
+        <v>-3.375409274255058</v>
       </c>
       <c r="G24">
-        <v>-6.347992085494071</v>
+        <v>-4.465235179127458</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-6.636505687228429</v>
       </c>
       <c r="E25">
-        <v>-26.11324818908238</v>
+        <v>-25.73520212197404</v>
       </c>
       <c r="F25">
-        <v>-3.034633835356591</v>
+        <v>-3.718898444765095</v>
       </c>
       <c r="G25">
-        <v>-6.631609832388973</v>
+        <v>-4.788721825951803</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-6.727984558402983</v>
       </c>
       <c r="E26">
-        <v>-26.62636052194349</v>
+        <v>-25.78916794672345</v>
       </c>
       <c r="F26">
-        <v>-2.589196660216616</v>
+        <v>-3.365888847694683</v>
       </c>
       <c r="G26">
-        <v>-6.56766333475241</v>
+        <v>-4.817073337950121</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-6.815911911923692</v>
       </c>
       <c r="E27">
-        <v>-27.43262361969115</v>
+        <v>-26.82737495466997</v>
       </c>
       <c r="F27">
-        <v>-3.043089809804369</v>
+        <v>-3.384906506528154</v>
       </c>
       <c r="G27">
-        <v>-7.893331569407086</v>
+        <v>-4.981822636711952</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-6.864534434112924</v>
       </c>
       <c r="E28">
-        <v>-26.23438939726157</v>
+        <v>-26.80216493986927</v>
       </c>
       <c r="F28">
-        <v>-2.932067868644165</v>
+        <v>-3.555120268822799</v>
       </c>
       <c r="G28">
-        <v>-7.482572321076474</v>
+        <v>-5.021036048624619</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-6.851278573430654</v>
       </c>
       <c r="E29">
-        <v>-26.77536995916589</v>
+        <v>-25.64820107933868</v>
       </c>
       <c r="F29">
-        <v>-3.133011576480464</v>
+        <v>-3.541570663215208</v>
       </c>
       <c r="G29">
-        <v>-7.497827314921436</v>
+        <v>-5.362532063182599</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-6.756323077112228</v>
       </c>
       <c r="E30">
-        <v>-26.4240962303909</v>
+        <v>-26.14503354814222</v>
       </c>
       <c r="F30">
-        <v>-3.360684215302894</v>
+        <v>-3.563049401602396</v>
       </c>
       <c r="G30">
-        <v>-6.883535726836431</v>
+        <v>-5.683204746298563</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.565154759345499</v>
       </c>
       <c r="E31">
-        <v>-25.44947352598608</v>
+        <v>-25.82656408507879</v>
       </c>
       <c r="F31">
-        <v>-3.128745484356046</v>
+        <v>-3.956466760581368</v>
       </c>
       <c r="G31">
-        <v>-7.427418632392216</v>
+        <v>-5.620158717048683</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.283201970575645</v>
       </c>
       <c r="E32">
-        <v>-25.16145352215023</v>
+        <v>-25.23108786696617</v>
       </c>
       <c r="F32">
-        <v>-3.052084223063966</v>
+        <v>-3.67355361313585</v>
       </c>
       <c r="G32">
-        <v>-7.162488915066501</v>
+        <v>-5.463808272319983</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.918581479983594</v>
       </c>
       <c r="E33">
-        <v>-24.89104928220421</v>
+        <v>-24.86867409213231</v>
       </c>
       <c r="F33">
-        <v>-3.268348586015041</v>
+        <v>-3.743833131956763</v>
       </c>
       <c r="G33">
-        <v>-7.056339582895308</v>
+        <v>-5.163372954085584</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.495905410871667</v>
       </c>
       <c r="E34">
-        <v>-23.39700608064559</v>
+        <v>-24.92506265047582</v>
       </c>
       <c r="F34">
-        <v>-3.40195182257556</v>
+        <v>-3.621982772107164</v>
       </c>
       <c r="G34">
-        <v>-6.916389580768159</v>
+        <v>-5.130029139414044</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.044447712502886</v>
       </c>
       <c r="E35">
-        <v>-24.2489388387606</v>
+        <v>-24.06614698544099</v>
       </c>
       <c r="F35">
-        <v>-3.482250445133332</v>
+        <v>-3.728254854579716</v>
       </c>
       <c r="G35">
-        <v>-7.368020824326613</v>
+        <v>-4.961886531474461</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.590538460368605</v>
       </c>
       <c r="E36">
-        <v>-23.69431398467118</v>
+        <v>-23.77022026598775</v>
       </c>
       <c r="F36">
-        <v>-3.11913890758578</v>
+        <v>-3.612092065317738</v>
       </c>
       <c r="G36">
-        <v>-6.600523809775216</v>
+        <v>-5.041670678970896</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.169063275720851</v>
       </c>
       <c r="E37">
-        <v>-24.64628073361562</v>
+        <v>-22.95567911775407</v>
       </c>
       <c r="F37">
-        <v>-3.468495404409846</v>
+        <v>-3.630350939610245</v>
       </c>
       <c r="G37">
-        <v>-6.412014725678036</v>
+        <v>-4.091547419745605</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.801261373450131</v>
       </c>
       <c r="E38">
-        <v>-22.6097897445742</v>
+        <v>-22.39456043193765</v>
       </c>
       <c r="F38">
-        <v>-3.204474832319977</v>
+        <v>-3.498937906462728</v>
       </c>
       <c r="G38">
-        <v>-6.147591521819828</v>
+        <v>-3.92136551575383</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.510525352800172</v>
       </c>
       <c r="E39">
-        <v>-22.17282370215207</v>
+        <v>-22.56794664474333</v>
       </c>
       <c r="F39">
-        <v>-3.246396021473451</v>
+        <v>-3.791284501891327</v>
       </c>
       <c r="G39">
-        <v>-6.06663875174803</v>
+        <v>-3.715730979582</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.313983664617899</v>
       </c>
       <c r="E40">
-        <v>-22.96404773772025</v>
+        <v>-21.96310554238284</v>
       </c>
       <c r="F40">
-        <v>-3.629001529111084</v>
+        <v>-3.847750994270558</v>
       </c>
       <c r="G40">
-        <v>-5.746072006089323</v>
+        <v>-3.407419873509674</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.212648409464276</v>
       </c>
       <c r="E41">
-        <v>-22.29979758485313</v>
+        <v>-21.29189965343995</v>
       </c>
       <c r="F41">
-        <v>-3.542526599198038</v>
+        <v>-3.719736752576728</v>
       </c>
       <c r="G41">
-        <v>-5.431186156576005</v>
+        <v>-2.953590427713145</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.210395585751195</v>
       </c>
       <c r="E42">
-        <v>-20.06759047767421</v>
+        <v>-20.62380935461433</v>
       </c>
       <c r="F42">
-        <v>-3.338195697051693</v>
+        <v>-3.808653709593227</v>
       </c>
       <c r="G42">
-        <v>-5.560357022427287</v>
+        <v>-3.210813195023437</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.292021252818312</v>
       </c>
       <c r="E43">
-        <v>-19.947617615789</v>
+        <v>-20.66469694642959</v>
       </c>
       <c r="F43">
-        <v>-3.699470744067238</v>
+        <v>-3.740045007823761</v>
       </c>
       <c r="G43">
-        <v>-5.668817115384891</v>
+        <v>-2.857316452885599</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.442794517837715</v>
       </c>
       <c r="E44">
-        <v>-20.00777386450689</v>
+        <v>-19.72996104108433</v>
       </c>
       <c r="F44">
-        <v>-2.984691564641809</v>
+        <v>-3.76259813873238</v>
       </c>
       <c r="G44">
-        <v>-4.931671182337532</v>
+        <v>-2.382527943279943</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.645376793881804</v>
       </c>
       <c r="E45">
-        <v>-19.38819710772545</v>
+        <v>-19.08554107589681</v>
       </c>
       <c r="F45">
-        <v>-3.931178360508705</v>
+        <v>-3.605858600611672</v>
       </c>
       <c r="G45">
-        <v>-5.138391577446243</v>
+        <v>-2.79780608627166</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.874374137762696</v>
       </c>
       <c r="E46">
-        <v>-19.40686800605907</v>
+        <v>-18.15219994054591</v>
       </c>
       <c r="F46">
-        <v>-3.648333967557619</v>
+        <v>-3.758235955989238</v>
       </c>
       <c r="G46">
-        <v>-5.807886512398595</v>
+        <v>-2.58372303788361</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.118905766069012</v>
       </c>
       <c r="E47">
-        <v>-17.74221907473548</v>
+        <v>-18.00860202976268</v>
       </c>
       <c r="F47">
-        <v>-3.988329084362648</v>
+        <v>-3.974486236694466</v>
       </c>
       <c r="G47">
-        <v>-5.390079112614874</v>
+        <v>-2.666638961460197</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.361434248360299</v>
       </c>
       <c r="E48">
-        <v>-17.10799723301323</v>
+        <v>-17.470949896254</v>
       </c>
       <c r="F48">
-        <v>-3.716869772995639</v>
+        <v>-4.168420299568274</v>
       </c>
       <c r="G48">
-        <v>-5.248341415896517</v>
+        <v>-1.969279164703799</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.593930463738362</v>
       </c>
       <c r="E49">
-        <v>-17.07569562791652</v>
+        <v>-17.2325483821202</v>
       </c>
       <c r="F49">
-        <v>-3.957000229188771</v>
+        <v>-4.107545235871345</v>
       </c>
       <c r="G49">
-        <v>-4.349253526704631</v>
+        <v>-2.72335853818453</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.815535419530904</v>
       </c>
       <c r="E50">
-        <v>-16.20319001238466</v>
+        <v>-16.29055786141465</v>
       </c>
       <c r="F50">
-        <v>-4.135191169572376</v>
+        <v>-4.08099606061162</v>
       </c>
       <c r="G50">
-        <v>-4.786119737157935</v>
+        <v>-2.605655402081282</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.022523430805801</v>
       </c>
       <c r="E51">
-        <v>-16.45432106695403</v>
+        <v>-16.10938720178978</v>
       </c>
       <c r="F51">
-        <v>-4.280775912246986</v>
+        <v>-4.197747819096988</v>
       </c>
       <c r="G51">
-        <v>-5.400705963795935</v>
+        <v>-2.387454035042379</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.228504750042776</v>
       </c>
       <c r="E52">
-        <v>-15.49978667324723</v>
+        <v>-15.43574499383076</v>
       </c>
       <c r="F52">
-        <v>-4.521475456845841</v>
+        <v>-4.343933956506032</v>
       </c>
       <c r="G52">
-        <v>-5.586629511826944</v>
+        <v>-2.436562667571927</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.439419548264194</v>
       </c>
       <c r="E53">
-        <v>-14.98654754311391</v>
+        <v>-14.41299819614643</v>
       </c>
       <c r="F53">
-        <v>-4.010003317456897</v>
+        <v>-4.174537792837949</v>
       </c>
       <c r="G53">
-        <v>-5.701826564956963</v>
+        <v>-2.954027419724328</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.664120039265453</v>
       </c>
       <c r="E54">
-        <v>-14.67594856787581</v>
+        <v>-14.58406130178617</v>
       </c>
       <c r="F54">
-        <v>-4.14762910612541</v>
+        <v>-4.371667697151759</v>
       </c>
       <c r="G54">
-        <v>-4.979045089004503</v>
+        <v>-2.678494025036326</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.913635929817988</v>
       </c>
       <c r="E55">
-        <v>-14.13435213350645</v>
+        <v>-14.19161468733344</v>
       </c>
       <c r="F55">
-        <v>-4.524884188708361</v>
+        <v>-4.536240277433339</v>
       </c>
       <c r="G55">
-        <v>-5.427292955021821</v>
+        <v>-2.996336191716214</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.186518107483047</v>
       </c>
       <c r="E56">
-        <v>-14.28686208113677</v>
+        <v>-13.4485283304668</v>
       </c>
       <c r="F56">
-        <v>-4.221258542723244</v>
+        <v>-4.402479651066289</v>
       </c>
       <c r="G56">
-        <v>-5.539811776810571</v>
+        <v>-3.07071421834702</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.493482713304046</v>
       </c>
       <c r="E57">
-        <v>-13.46387532887879</v>
+        <v>-13.07911353481708</v>
       </c>
       <c r="F57">
-        <v>-4.536561683985625</v>
+        <v>-4.61599383424007</v>
       </c>
       <c r="G57">
-        <v>-4.953156622887402</v>
+        <v>-2.663242341736904</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.830692975597028</v>
       </c>
       <c r="E58">
-        <v>-13.60872762696215</v>
+        <v>-12.17164809994601</v>
       </c>
       <c r="F58">
-        <v>-4.370089657249426</v>
+        <v>-4.698863709216132</v>
       </c>
       <c r="G58">
-        <v>-5.927695155464819</v>
+        <v>-2.844736379836369</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.194117748132164</v>
       </c>
       <c r="E59">
-        <v>-12.09153033780231</v>
+        <v>-11.84280390293101</v>
       </c>
       <c r="F59">
-        <v>-4.50915100662699</v>
+        <v>-4.485734716884654</v>
       </c>
       <c r="G59">
-        <v>-5.948323164720017</v>
+        <v>-3.016222638770616</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.584368975476441</v>
       </c>
       <c r="E60">
-        <v>-11.96671200872889</v>
+        <v>-11.85518475086798</v>
       </c>
       <c r="F60">
-        <v>-4.664155943406236</v>
+        <v>-4.745296187245254</v>
       </c>
       <c r="G60">
-        <v>-5.271730420131468</v>
+        <v>-2.855555242658707</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.988107761513886</v>
       </c>
       <c r="E61">
-        <v>-12.75274188461027</v>
+        <v>-11.46339476514637</v>
       </c>
       <c r="F61">
-        <v>-4.880372261047949</v>
+        <v>-4.426296042264178</v>
       </c>
       <c r="G61">
-        <v>-5.574373872240562</v>
+        <v>-3.148353132334007</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.410265980918316</v>
       </c>
       <c r="E62">
-        <v>-11.26819942151974</v>
+        <v>-11.48222416007026</v>
       </c>
       <c r="F62">
-        <v>-4.657482615609283</v>
+        <v>-4.786017072032071</v>
       </c>
       <c r="G62">
-        <v>-5.665162273109535</v>
+        <v>-3.339232567037306</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.842877553670784</v>
       </c>
       <c r="E63">
-        <v>-11.09638458919472</v>
+        <v>-11.62000751022764</v>
       </c>
       <c r="F63">
-        <v>-4.728985633084131</v>
+        <v>-4.635217756556838</v>
       </c>
       <c r="G63">
-        <v>-6.350031381546262</v>
+        <v>-3.857852699582912</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.27854666114197</v>
       </c>
       <c r="E64">
-        <v>-11.93846338786904</v>
+        <v>-10.63994610853961</v>
       </c>
       <c r="F64">
-        <v>-4.775568873980562</v>
+        <v>-4.920308681904316</v>
       </c>
       <c r="G64">
-        <v>-6.663867788123631</v>
+        <v>-3.67112468898586</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.718752291598362</v>
       </c>
       <c r="E65">
-        <v>-9.834842300137916</v>
+        <v>-10.49461379221144</v>
       </c>
       <c r="F65">
-        <v>-4.911550353354517</v>
+        <v>-4.613685174288467</v>
       </c>
       <c r="G65">
-        <v>-6.308970685222681</v>
+        <v>-3.933306653513981</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.14728448707244</v>
       </c>
       <c r="E66">
-        <v>-10.74626562129169</v>
+        <v>-10.05176979052735</v>
       </c>
       <c r="F66">
-        <v>-4.996038858235649</v>
+        <v>-4.791971376923394</v>
       </c>
       <c r="G66">
-        <v>-6.748061582278376</v>
+        <v>-4.359814166974906</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.56526879594913</v>
       </c>
       <c r="E67">
-        <v>-10.90950805232019</v>
+        <v>-9.719891515927211</v>
       </c>
       <c r="F67">
-        <v>-5.033161315024707</v>
+        <v>-4.669673698676283</v>
       </c>
       <c r="G67">
-        <v>-6.181875531424521</v>
+        <v>-4.151378909276852</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.96042362836179</v>
       </c>
       <c r="E68">
-        <v>-10.92808385269965</v>
+        <v>-10.12482313321909</v>
       </c>
       <c r="F68">
-        <v>-4.751436046434804</v>
+        <v>-4.782659698948525</v>
       </c>
       <c r="G68">
-        <v>-6.195862586327942</v>
+        <v>-3.830461245790982</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-11.31836287133578</v>
       </c>
       <c r="E69">
-        <v>-10.21287478182423</v>
+        <v>-9.283301336847712</v>
       </c>
       <c r="F69">
-        <v>-5.33699902306494</v>
+        <v>-4.810647748386912</v>
       </c>
       <c r="G69">
-        <v>-7.135249746369377</v>
+        <v>-4.246464398255799</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-11.63724319664139</v>
       </c>
       <c r="E70">
-        <v>-10.50905056734789</v>
+        <v>-9.200688385525781</v>
       </c>
       <c r="F70">
-        <v>-4.779228601166129</v>
+        <v>-4.969275964186004</v>
       </c>
       <c r="G70">
-        <v>-7.227531203276561</v>
+        <v>-4.363012153965842</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-11.89940565920879</v>
       </c>
       <c r="E71">
-        <v>-10.96298933035078</v>
+        <v>-9.794240002185143</v>
       </c>
       <c r="F71">
-        <v>-5.38322109577375</v>
+        <v>-4.967479235289331</v>
       </c>
       <c r="G71">
-        <v>-6.957119222537812</v>
+        <v>-4.55084588677301</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-12.1074526006295</v>
       </c>
       <c r="E72">
-        <v>-11.73126758812209</v>
+        <v>-9.936538240928169</v>
       </c>
       <c r="F72">
-        <v>-5.221016817896773</v>
+        <v>-4.98057241045798</v>
       </c>
       <c r="G72">
-        <v>-5.987255180261847</v>
+        <v>-4.384193024326099</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-12.2559502811842</v>
       </c>
       <c r="E73">
-        <v>-10.90771477661315</v>
+        <v>-9.897321656021743</v>
       </c>
       <c r="F73">
-        <v>-5.212051397496274</v>
+        <v>-5.066759896882255</v>
       </c>
       <c r="G73">
-        <v>-6.447265414580196</v>
+        <v>-4.247974007021708</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-12.33692007090555</v>
       </c>
       <c r="E74">
-        <v>-11.27145992280527</v>
+        <v>-9.944653266349913</v>
       </c>
       <c r="F74">
-        <v>-5.508517464018994</v>
+        <v>-5.064383310803623</v>
       </c>
       <c r="G74">
-        <v>-5.988761478482215</v>
+        <v>-4.234629197952906</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-12.35797363285432</v>
       </c>
       <c r="E75">
-        <v>-10.62695844508561</v>
+        <v>-10.18289175541944</v>
       </c>
       <c r="F75">
-        <v>-5.276237445702193</v>
+        <v>-5.308629924621266</v>
       </c>
       <c r="G75">
-        <v>-6.101502106822095</v>
+        <v>-3.808383217589583</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-12.30950792453089</v>
       </c>
       <c r="E76">
-        <v>-12.13109108673332</v>
+        <v>-11.26784167207314</v>
       </c>
       <c r="F76">
-        <v>-5.498714564174265</v>
+        <v>-5.454769673455751</v>
       </c>
       <c r="G76">
-        <v>-6.253340277980768</v>
+        <v>-3.482231581606125</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-12.20180180838753</v>
       </c>
       <c r="E77">
-        <v>-11.67215741689997</v>
+        <v>-10.73513463218084</v>
       </c>
       <c r="F77">
-        <v>-5.604948541746288</v>
+        <v>-5.309445866513023</v>
       </c>
       <c r="G77">
-        <v>-6.191356933848994</v>
+        <v>-3.32495087358089</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-12.04054368042562</v>
       </c>
       <c r="E78">
-        <v>-12.18939971805608</v>
+        <v>-11.44318418565014</v>
       </c>
       <c r="F78">
-        <v>-5.47720103435616</v>
+        <v>-5.449553443920323</v>
       </c>
       <c r="G78">
-        <v>-6.132339838520406</v>
+        <v>-3.380597833550499</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-11.82716512961283</v>
       </c>
       <c r="E79">
-        <v>-12.95205361110987</v>
+        <v>-11.99213939028196</v>
       </c>
       <c r="F79">
-        <v>-5.621925931666664</v>
+        <v>-5.57444805397521</v>
       </c>
       <c r="G79">
-        <v>-5.600805267826103</v>
+        <v>-3.107885023661957</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-11.58414974206595</v>
       </c>
       <c r="E80">
-        <v>-14.66440095915625</v>
+        <v>-12.06238507908894</v>
       </c>
       <c r="F80">
-        <v>-5.712304957149104</v>
+        <v>-5.749206239841613</v>
       </c>
       <c r="G80">
-        <v>-4.693699237338102</v>
+        <v>-3.009810112061048</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-11.3163236044399</v>
       </c>
       <c r="E81">
-        <v>-14.10552839644763</v>
+        <v>-13.23343487205047</v>
       </c>
       <c r="F81">
-        <v>-5.708391749538279</v>
+        <v>-5.514070010719959</v>
       </c>
       <c r="G81">
-        <v>-4.94967061843455</v>
+        <v>-2.76387630503967</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-11.04684608581951</v>
       </c>
       <c r="E82">
-        <v>-14.71712145355355</v>
+        <v>-13.83022887609933</v>
       </c>
       <c r="F82">
-        <v>-5.673898530885707</v>
+        <v>-5.870213321675163</v>
       </c>
       <c r="G82">
-        <v>-5.173605850347471</v>
+        <v>-2.960704790077038</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-10.7946197976836</v>
       </c>
       <c r="E83">
-        <v>-16.32142394025093</v>
+        <v>-15.13205646992837</v>
       </c>
       <c r="F83">
-        <v>-6.054534180839483</v>
+        <v>-6.234421617664021</v>
       </c>
       <c r="G83">
-        <v>-5.164544887206485</v>
+        <v>-2.306961430800539</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-10.56741450173821</v>
       </c>
       <c r="E84">
-        <v>-16.3622617188521</v>
+        <v>-15.20461620895327</v>
       </c>
       <c r="F84">
-        <v>-5.812771012495434</v>
+        <v>-6.095666764225492</v>
       </c>
       <c r="G84">
-        <v>-4.917823170346761</v>
+        <v>-2.96228723084481</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-10.38998243833811</v>
       </c>
       <c r="E85">
-        <v>-17.13770855097756</v>
+        <v>-16.14667918524295</v>
       </c>
       <c r="F85">
-        <v>-6.089264312569255</v>
+        <v>-6.528496601678561</v>
       </c>
       <c r="G85">
-        <v>-4.528066022917286</v>
+        <v>-2.734525008288491</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-10.25974163813619</v>
       </c>
       <c r="E86">
-        <v>-19.06624071967612</v>
+        <v>-17.5102117659005</v>
       </c>
       <c r="F86">
-        <v>-6.343263710003757</v>
+        <v>-6.069407517556749</v>
       </c>
       <c r="G86">
-        <v>-4.546290576110973</v>
+        <v>-2.025915977789651</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-10.18432844017459</v>
       </c>
       <c r="E87">
-        <v>-20.21544968249865</v>
+        <v>-19.28610718969653</v>
       </c>
       <c r="F87">
-        <v>-6.420475007251297</v>
+        <v>-6.204890319754218</v>
       </c>
       <c r="G87">
-        <v>-4.203215431330761</v>
+        <v>-1.869244410143642</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-10.16377299067455</v>
       </c>
       <c r="E88">
-        <v>-21.03527103142527</v>
+        <v>-20.30156767270252</v>
       </c>
       <c r="F88">
-        <v>-6.345253448505282</v>
+        <v>-6.251219666041691</v>
       </c>
       <c r="G88">
-        <v>-4.455313474146262</v>
+        <v>-1.778522220185454</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-10.18091182585834</v>
       </c>
       <c r="E89">
-        <v>-22.50704319781417</v>
+        <v>-20.8555766543269</v>
       </c>
       <c r="F89">
-        <v>-6.697718808192055</v>
+        <v>-6.292225095031371</v>
       </c>
       <c r="G89">
-        <v>-4.442617532003156</v>
+        <v>-2.003765117586387</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-10.23869176475172</v>
       </c>
       <c r="E90">
-        <v>-24.44361340787634</v>
+        <v>-22.79874937949226</v>
       </c>
       <c r="F90">
-        <v>-6.47676464319003</v>
+        <v>-6.482124594469845</v>
       </c>
       <c r="G90">
-        <v>-5.382335746598519</v>
+        <v>-2.374043015062791</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-10.31760601112137</v>
       </c>
       <c r="E91">
-        <v>-24.86764160005857</v>
+        <v>-25.06818054301424</v>
       </c>
       <c r="F91">
-        <v>-6.32933346957458</v>
+        <v>-6.36632380176289</v>
       </c>
       <c r="G91">
-        <v>-4.169537251559755</v>
+        <v>-2.971503789626141</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-10.40957039702974</v>
       </c>
       <c r="E92">
-        <v>-27.83660425744141</v>
+        <v>-26.70734322262266</v>
       </c>
       <c r="F92">
-        <v>-6.646030753175872</v>
+        <v>-6.71554817398621</v>
       </c>
       <c r="G92">
-        <v>-5.519481716653907</v>
+        <v>-2.59848476044322</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-10.50567237060767</v>
       </c>
       <c r="E93">
-        <v>-30.18185566127381</v>
+        <v>-28.48607799962149</v>
       </c>
       <c r="F93">
-        <v>-6.602989611293814</v>
+        <v>-6.462272769661754</v>
       </c>
       <c r="G93">
-        <v>-5.090388667126811</v>
+        <v>-2.657256875401902</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-10.58285752841173</v>
       </c>
       <c r="E94">
-        <v>-31.73117568080706</v>
+        <v>-30.764677058772</v>
       </c>
       <c r="F94">
-        <v>-6.838571916261874</v>
+        <v>-6.321987507446554</v>
       </c>
       <c r="G94">
-        <v>-4.779419192986451</v>
+        <v>-3.004552965744685</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-10.64221379303733</v>
       </c>
       <c r="E95">
-        <v>-34.18134050621217</v>
+        <v>-33.22552908283521</v>
       </c>
       <c r="F95">
-        <v>-6.549887947304754</v>
+        <v>-6.291354480891028</v>
       </c>
       <c r="G95">
-        <v>-6.530575293075955</v>
+        <v>-3.535196999688925</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-10.66281035473454</v>
       </c>
       <c r="E96">
-        <v>-36.50733457432695</v>
+        <v>-35.77337082834875</v>
       </c>
       <c r="F96">
-        <v>-6.621160678641623</v>
+        <v>-6.336350569843694</v>
       </c>
       <c r="G96">
-        <v>-6.122570418634017</v>
+        <v>-4.238502536233852</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-10.64169172746307</v>
       </c>
       <c r="E97">
-        <v>-37.46530381556856</v>
+        <v>-38.29338510108517</v>
       </c>
       <c r="F97">
-        <v>-6.614746629841747</v>
+        <v>-6.349088375396542</v>
       </c>
       <c r="G97">
-        <v>-6.829431481088123</v>
+        <v>-4.347220851743518</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.57094588467407</v>
       </c>
       <c r="E98">
-        <v>-40.8304671923565</v>
+        <v>-40.24964964460671</v>
       </c>
       <c r="F98">
-        <v>-6.980191264179283</v>
+        <v>-6.225770148509183</v>
       </c>
       <c r="G98">
-        <v>-6.891550557587007</v>
+        <v>-5.033897518044687</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.44866055303218</v>
       </c>
       <c r="E99">
-        <v>-43.22527368725483</v>
+        <v>-42.92703291758367</v>
       </c>
       <c r="F99">
-        <v>-7.043366289970087</v>
+        <v>-6.176372943545442</v>
       </c>
       <c r="G99">
-        <v>-6.781183590398784</v>
+        <v>-5.808763806966502</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-10.27108346356404</v>
       </c>
       <c r="E100">
-        <v>-44.28849372138272</v>
+        <v>-45.6095288377153</v>
       </c>
       <c r="F100">
-        <v>-7.083765354020917</v>
+        <v>-6.300446641504156</v>
       </c>
       <c r="G100">
-        <v>-7.541989992415314</v>
+        <v>-6.105183433461765</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-10.06640860030911</v>
       </c>
       <c r="E101">
-        <v>-47.5875594915547</v>
+        <v>-47.49323817068594</v>
       </c>
       <c r="F101">
-        <v>-7.059598149227943</v>
+        <v>-6.312893690098621</v>
       </c>
       <c r="G101">
-        <v>-8.114929556169281</v>
+        <v>-6.127665348218955</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.799183161809962</v>
       </c>
       <c r="E102">
-        <v>-50.31197889193084</v>
+        <v>-49.88540456523781</v>
       </c>
       <c r="F102">
-        <v>-6.926733816390722</v>
+        <v>-5.932544655266214</v>
       </c>
       <c r="G102">
-        <v>-8.666006277181902</v>
+        <v>-6.907275648898545</v>
       </c>
     </row>
   </sheetData>
